--- a/E/R088.xlsx
+++ b/E/R088.xlsx
@@ -11,29 +11,35 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="48">
   <si>
     <t/>
   </si>
   <si>
+    <t>20056971</t>
+  </si>
+  <si>
+    <t>TUMBLER BUAVITA PCS</t>
+  </si>
+  <si>
+    <t>R088</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
     <t>20060469</t>
   </si>
   <si>
     <t>TAS COCA COLA</t>
   </si>
   <si>
-    <t>R088</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
-    <t>PT</t>
-  </si>
-  <si>
     <t>20067618</t>
   </si>
   <si>
@@ -145,31 +151,10 @@
     <t>KIN PHOTOCARD JKT48</t>
   </si>
   <si>
-    <t>20140198</t>
-  </si>
-  <si>
-    <t>FIESTA TREASURE P/C</t>
-  </si>
-  <si>
-    <t>RT,(E-7H)</t>
-  </si>
-  <si>
     <t>20140668</t>
   </si>
   <si>
     <t>KIN PTCARD JKT48 SRS</t>
-  </si>
-  <si>
-    <t>20141232</t>
-  </si>
-  <si>
-    <t>FIESTA STANDEE TREAS</t>
-  </si>
-  <si>
-    <t>20142688</t>
-  </si>
-  <si>
-    <t>FIESTA X TREASURE PC</t>
   </si>
 </sst>
 </file>
@@ -562,7 +547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -607,210 +592,210 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F12" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -824,13 +809,13 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -844,13 +829,13 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -864,13 +849,13 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -884,73 +869,33 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/E/R088.xlsx
+++ b/E/R088.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="53">
   <si>
     <t/>
   </si>
@@ -143,6 +143,21 @@
   </si>
   <si>
     <t xml:space="preserve">IDM COSMETIC </t>
+  </si>
+  <si>
+    <t>20144186</t>
+  </si>
+  <si>
+    <t>REXONA ARCTICSEA7ML</t>
+  </si>
+  <si>
+    <t>PT,(E-27H)</t>
+  </si>
+  <si>
+    <t>20144189</t>
+  </si>
+  <si>
+    <t>REXONA FROZEN ENGLI7</t>
   </si>
   <si>
     <t>20139151</t>
@@ -547,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -555,7 +570,7 @@
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -869,32 +884,72 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>12</v>
       </c>
     </row>
